--- a/DataSets/Talisay community data.xlsx
+++ b/DataSets/Talisay community data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\DataSets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\DataSets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEABEA7-AA72-49E2-BB57-E30BEDD739A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE8BA03-1E5E-4E26-AA8E-C8C21E7B066A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8208" yWindow="1608" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0000000000000"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -110,6 +113,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -119,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -127,11 +145,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -139,6 +172,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -361,11 +399,13 @@
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.44140625" customWidth="1"/>
     <col min="5" max="5" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -388,15 +428,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
-        <v>14.098746589999999</v>
-      </c>
-      <c r="C2">
-        <v>121.0404358</v>
+      <c r="B2" s="4">
+        <v>14.0988307789674</v>
+      </c>
+      <c r="C2" s="4">
+        <v>121.040374479175</v>
       </c>
       <c r="D2">
         <v>6215</v>
@@ -409,15 +449,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3">
-        <v>13.993172250000001</v>
-      </c>
-      <c r="C3">
-        <v>121.08436690000001</v>
+      <c r="B3" s="5">
+        <v>14.0924299518478</v>
+      </c>
+      <c r="C3" s="5">
+        <v>121.012740049122</v>
       </c>
       <c r="D3">
         <v>5116</v>
@@ -430,15 +470,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4">
-        <v>14.091027265000001</v>
-      </c>
-      <c r="C4">
-        <v>120.97646930000001</v>
+      <c r="B4" s="4">
+        <v>14.087717319131</v>
+      </c>
+      <c r="C4" s="4">
+        <v>120.981125830484</v>
       </c>
       <c r="D4">
         <v>3258</v>
@@ -451,15 +491,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
-        <v>14.09134708</v>
-      </c>
-      <c r="C5">
-        <v>121.02366499999999</v>
+      <c r="B5" s="4">
+        <v>14.093728866395001</v>
+      </c>
+      <c r="C5" s="4">
+        <v>121.023238610025</v>
       </c>
       <c r="D5">
         <v>1921</v>
@@ -472,15 +512,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
-        <v>14.082114669999999</v>
-      </c>
-      <c r="C6">
-        <v>121.1480796</v>
+      <c r="B6" s="4">
+        <v>14.094627769658301</v>
+      </c>
+      <c r="C6" s="4">
+        <v>121.02095804005999</v>
       </c>
       <c r="D6">
         <v>265</v>
@@ -493,15 +533,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
-        <v>14.0910806</v>
-      </c>
-      <c r="C7">
-        <v>121.0238124</v>
+      <c r="B7" s="4">
+        <v>14.0906034046505</v>
+      </c>
+      <c r="C7" s="4">
+        <v>121.02241006916501</v>
       </c>
       <c r="D7">
         <v>8073</v>
@@ -514,15 +554,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8">
-        <v>14.099348693333333</v>
-      </c>
-      <c r="C8">
-        <v>121.02714666666667</v>
+      <c r="B8" s="4">
+        <v>14.093636629279301</v>
+      </c>
+      <c r="C8" s="4">
+        <v>121.02892975410801</v>
       </c>
       <c r="D8">
         <v>9050</v>
@@ -535,15 +575,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>14.086697129999999</v>
-      </c>
-      <c r="C9">
-        <v>120.97180349999999</v>
+      <c r="B9" s="4">
+        <v>14.0866354122453</v>
+      </c>
+      <c r="C9" s="4">
+        <v>120.97178897009999</v>
       </c>
       <c r="D9">
         <v>4531</v>
@@ -556,15 +596,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10">
-        <v>14.084433813333334</v>
-      </c>
-      <c r="C10">
-        <v>120.99547663333334</v>
+      <c r="B10" s="4">
+        <v>14.0821277611019</v>
+      </c>
+      <c r="C10" s="4">
+        <v>120.99648880771799</v>
       </c>
       <c r="D10">
         <v>3922</v>
@@ -577,15 +617,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11">
-        <v>14.11908639</v>
-      </c>
-      <c r="C11">
-        <v>121.0574388</v>
+      <c r="B11" s="4">
+        <v>14.119086389067199</v>
+      </c>
+      <c r="C11" s="4">
+        <v>121.057438810634</v>
       </c>
       <c r="D11">
         <v>2950</v>
@@ -600,6 +640,9 @@
     </row>
     <row r="12" spans="1:7" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:7" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+    </row>
     <row r="15" spans="1:7" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="26" spans="4:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="D26" s="2"/>
